--- a/Koszta.xlsx
+++ b/Koszta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00547987-3A69-468F-A270-905C7FD3554E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AD7302-DC79-468B-95C2-7ADF93FB9E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{C42FA279-E8B3-4402-922D-DA72FD085F98}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
   <si>
     <t>Data</t>
   </si>
@@ -132,6 +132,9 @@
   </si>
   <si>
     <t>Razem:</t>
+  </si>
+  <si>
+    <t>pr-360-st-2885 dc motor 3pcs</t>
   </si>
 </sst>
 </file>
@@ -316,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -360,6 +363,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -821,7 +825,7 @@
       </c>
       <c r="H1" s="24">
         <f>SUM(Tabela2[[#All],[Koszt]])</f>
-        <v>455.65999999999997</v>
+        <v>505.02</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1034,7 +1038,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>46119</v>
       </c>
@@ -1048,7 +1052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>46119</v>
       </c>
@@ -1062,7 +1066,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>46119</v>
       </c>
@@ -1076,7 +1080,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>46119</v>
       </c>
@@ -1090,7 +1094,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>46119</v>
       </c>
@@ -1104,7 +1108,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>46119</v>
       </c>
@@ -1118,7 +1122,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>46119</v>
       </c>
@@ -1132,7 +1136,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>46119</v>
       </c>
@@ -1146,7 +1150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>46120</v>
       </c>
@@ -1159,6 +1163,23 @@
       <c r="D25" s="9" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B26" s="7">
+        <v>49.36</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="25"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="10"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B56" s="12"/>

--- a/Koszta.xlsx
+++ b/Koszta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79AD7302-DC79-468B-95C2-7ADF93FB9E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B2C97D-B87F-4206-B28F-9667C6A1B091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{C42FA279-E8B3-4402-922D-DA72FD085F98}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="35">
   <si>
     <t>Data</t>
   </si>
@@ -135,6 +135,12 @@
   </si>
   <si>
     <t>pr-360-st-2885 dc motor 3pcs</t>
+  </si>
+  <si>
+    <t>koszulka</t>
+  </si>
+  <si>
+    <t>gabirela</t>
   </si>
 </sst>
 </file>
@@ -825,7 +831,7 @@
       </c>
       <c r="H1" s="24">
         <f>SUM(Tabela2[[#All],[Koszt]])</f>
-        <v>505.02</v>
+        <v>575.02</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1180,6 +1186,20 @@
       <c r="E26" s="25"/>
       <c r="F26" s="9"/>
       <c r="G26" s="10"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B27" s="7">
+        <v>70</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B56" s="12"/>

--- a/Koszta.xlsx
+++ b/Koszta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tech\robotyka\robots\evangelion-turbo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B2C97D-B87F-4206-B28F-9667C6A1B091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1006FF-6536-4C07-9EF9-F141F83E609B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{C42FA279-E8B3-4402-922D-DA72FD085F98}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="37">
   <si>
     <t>Data</t>
   </si>
@@ -141,6 +141,12 @@
   </si>
   <si>
     <t>gabirela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">przody metalowe </t>
+  </si>
+  <si>
+    <t>mateu</t>
   </si>
 </sst>
 </file>
@@ -831,7 +837,7 @@
       </c>
       <c r="H1" s="24">
         <f>SUM(Tabela2[[#All],[Koszt]])</f>
-        <v>575.02</v>
+        <v>635.02</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1199,6 +1205,20 @@
       </c>
       <c r="D27" s="9" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>46132</v>
+      </c>
+      <c r="B28" s="7">
+        <v>60</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
